--- a/forms/trg/Formulir_TRG_build-acoustics.xlsx
+++ b/forms/trg/Formulir_TRG_build-acoustics.xlsx
@@ -916,7 +916,11 @@
           <t>Dr. Eng. Ir. Asniawaty, ST., MT</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Dr. Asniawaty is an Associate Professor in the Department of Architecture, Faculty of Engineering, Hasanuddin University, Makassar, Indonesia. She is a member of the Building Science and Technology Laboratory and part of the Advanced Facade and Daylighting Systems as well as the Building Acoustics Research Group. She earned her Bachelor's degree in Architecture from Hasanuddin University (1997), her Master's degree in Architecture from the Faculty of Engineering, Gadjah Mada University, Yogyakarta (2000), and her Doctorate degree in Architecture and Mechatronics from the Faculty of Engineering, Oita University, Japan (2014). Her research focuses primarily on Building Science and Technology, specifically building acoustics with an emphasis on materials, buildings, and environmental aspects.</t>
@@ -947,7 +951,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -980,7 +984,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1017,7 +1021,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1050,7 +1054,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1087,7 +1091,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1124,7 +1128,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1161,7 +1165,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1194,7 +1198,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1227,7 +1231,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1260,7 +1264,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -1293,7 +1297,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -1326,7 +1330,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1359,7 +1363,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -1392,7 +1396,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="12" t="n"/>
